--- a/GunfireDungeon_Godot/excel/ActivePropBase@主动道具.xlsx
+++ b/GunfireDungeon_Godot/excel/ActivePropBase@主动道具.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28290" windowHeight="13050"/>
+    <workbookView windowWidth="24765" windowHeight="12495"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="63">
   <si>
     <t>Id</t>
   </si>
@@ -127,6 +127,9 @@
     <t>uint</t>
   </si>
   <si>
+    <t>5000</t>
+  </si>
+  <si>
     <t>医药箱</t>
   </si>
   <si>
@@ -139,6 +142,9 @@
     <t>"ChangeHp":[2]</t>
   </si>
   <si>
+    <t>5001</t>
+  </si>
+  <si>
     <t>弹药箱</t>
   </si>
   <si>
@@ -151,6 +157,9 @@
     <t>"TotalAmmo":[]</t>
   </si>
   <si>
+    <t>5002</t>
+  </si>
+  <si>
     <t>猪猪存钱罐</t>
   </si>
   <si>
@@ -160,6 +169,9 @@
     <t>"PiggyBank":[2]</t>
   </si>
   <si>
+    <t>5003</t>
+  </si>
+  <si>
     <t>红外遥控器</t>
   </si>
   <si>
@@ -172,6 +184,9 @@
     <t>"Hurt":[250]</t>
   </si>
   <si>
+    <t>5004</t>
+  </si>
+  <si>
     <t>魔术棒</t>
   </si>
   <si>
@@ -182,6 +197,9 @@
   </si>
   <si>
     <t>"EnterRoom":[0.5]</t>
+  </si>
+  <si>
+    <t>5005</t>
   </si>
   <si>
     <t>便携式供血器</t>
@@ -199,6 +217,9 @@
   </si>
   <si>
     <t>"EnterRoom":[1]</t>
+  </si>
+  <si>
+    <t>5006</t>
   </si>
   <si>
     <t>便携式献血器</t>
@@ -1326,18 +1347,21 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" ht="33" customHeight="1" spans="2:11">
+    <row r="4" ht="33" customHeight="1" spans="1:11">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="B4" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="3">
         <v>0</v>
@@ -1352,18 +1376,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="33" customHeight="1" spans="2:11">
+    <row r="5" ht="33" customHeight="1" spans="1:11">
+      <c r="A5" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="B5" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H5" s="3">
         <v>0</v>
@@ -1378,15 +1405,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="33" customHeight="1" spans="2:11">
+    <row r="6" ht="33" customHeight="1" spans="1:11">
+      <c r="A6" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H6" s="3">
         <v>0</v>
@@ -1401,18 +1431,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="33" customHeight="1" spans="2:11">
+    <row r="7" ht="33" customHeight="1" spans="1:11">
+      <c r="A7" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H7" s="3">
         <v>6</v>
@@ -1427,18 +1460,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" ht="33" customHeight="1" spans="2:11">
+    <row r="8" ht="33" customHeight="1" spans="1:11">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="B8" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="H8" s="3">
         <v>0</v>
@@ -1453,21 +1489,24 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="57" customHeight="1" spans="2:11">
+    <row r="9" ht="57" customHeight="1" spans="1:11">
+      <c r="A9" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="B9" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="H9" s="3">
         <v>0</v>
@@ -1482,18 +1521,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" ht="57" customHeight="1" spans="2:11">
+    <row r="10" ht="57" customHeight="1" spans="1:11">
+      <c r="A10" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="B10" s="4" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H10" s="3">
         <v>0</v>
